--- a/data/trans_dic/IP07_C14_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C14_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 33,67</t>
+          <t>0,0; 48,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,58</t>
+          <t>2,29; 30,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 33,67</t>
+          <t>4,36; 33,57</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 19,41</t>
+          <t>6,74; 15,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 16,21</t>
+          <t>11,26; 21,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,7; 16,03</t>
+          <t>9,82; 16,44</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 21,23</t>
+          <t>11,82; 32,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,84; 35,43</t>
+          <t>4,25; 22,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,62; 24,92</t>
+          <t>9,94; 24,58</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 18,09</t>
+          <t>8,94; 17,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 18,41</t>
+          <t>11,18; 19,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 16,33</t>
+          <t>10,57; 16,58</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3576</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>360; 3677</t>
+          <t>0; 7440</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7361</t>
+          <t>282; 3710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1316; 8778</t>
+          <t>1200; 9244</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21441</t>
+          <t>19732</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20833</t>
+          <t>21813</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42274</t>
+          <t>41545</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11128; 29915</t>
+          <t>12661; 28438</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13244; 30831</t>
+          <t>15456; 29367</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29944; 55190</t>
+          <t>31893; 53433</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13732</t>
+          <t>13763</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1461; 7829</t>
+          <t>5454; 14773</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5846; 16137</t>
+          <t>1658; 8587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8758; 20543</t>
+          <t>8458; 20927</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>31593</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>33400</t>
+          <t>27291</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59948</t>
+          <t>58883</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16535; 36535</t>
+          <t>22255; 42528</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24269; 46183</t>
+          <t>21073; 36454</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45397; 73927</t>
+          <t>46261; 72535</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP07_C14_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C14_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores en cuyo colegio/instituto se han producido situaciones de cyberbulling (tasa de respuesta: 94,11%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>15,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 48,92</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2,29; 30,1</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4,36; 33,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6,74; 15,15</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11,26; 21,4</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9,82; 16,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>20,76%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10,73%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>11,82; 32,02</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4,25; 22,03</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9,94; 24,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>8,94; 17,07</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11,18; 19,34</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10,57; 16,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1499988661308798</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1050520149025543</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1298802536933712</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2281</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3576</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.02290344279064322</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.04359531322982902</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0; 7440</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>282; 3710</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1200; 9244</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.4891644780609729</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.3010235749904515</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.3357457069587781</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1051142412036891</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1589820660701184</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.127860927831707</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19732</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>21813</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>41545</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.06744792815992931</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1126479746974654</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.09815497422932577</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>12661; 28438</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>15456; 29367</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31893; 53433</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.151496648395968</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2140380125692732</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1644482503264069</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2076141331589866</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1073051671538781</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1616784479810715</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>9580</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4183</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13763</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1181902831624015</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.04253758245750938</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.09936346675152702</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5454; 14773</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1658; 8587</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8458; 20927</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.3201628243524539</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.220272774217604</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2458447416605768</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.126844091474199</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1447701304171976</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.134566677027244</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>31593</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>27291</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>58883</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.08935487176589624</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1117886073694327</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1057216195365285</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>22255; 42528</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>21073; 36454</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>46261; 72535</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1707497838914276</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.193378280641898</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1657644140181148</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores en cuyo colegio/instituto se han producido situaciones de cyberbulling (tasa de respuesta: 94,11%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2281</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1295</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>3576</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>282</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>7440</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3710</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>9244</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>19732</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>21813</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>41545</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>12661</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>15456</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>31893</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>28438</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>29367</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>53433</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>9580</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>4183</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>13763</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>5454</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1658</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>8458</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>14773</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>8587</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>20927</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>31593</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>27291</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>58883</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>22255</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>21073</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>42528</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>36454</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>72535</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>